--- a/build/simple-flow/SimpleFlow_SpecRecheck_ChangeList_2026-07-23.xlsx
+++ b/build/simple-flow/SimpleFlow_SpecRecheck_ChangeList_2026-07-23.xlsx
@@ -18,7 +18,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="3">
+  <fonts count="4">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -29,6 +29,10 @@
     <font>
       <b val="1"/>
       <sz val="13"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00C00000"/>
     </font>
     <font>
       <b val="1"/>
@@ -79,10 +83,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -456,7 +461,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G8"/>
+  <dimension ref="A1:G9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -476,118 +481,88 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>PROVISIONAL — column D 'What needs to change' is pending a fresh LIVE staging check (needs current cookies); it will be rewritten to observed build behaviour before sign-off.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
         <is>
           <t>The other 180 cases need no change (151 Verified, 21 Blocked-on-environment, 4 to re-verify live, 3 retired, plus 4 Create-Purchase-Orders cases deleted from TestRail and ignored per your ruling). Nothing pushed to TestRail yet.  Orange rows = waiting on a ticket that is NOT yet done.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>Case ID</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>TestRail link</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>Area</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>What needs to change</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>Driving ticket</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>Ticket status</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>Action</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
+          <t>Case ID</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>TestRail link</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>Area</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>What needs to change</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
+          <t>Driving ticket</t>
+        </is>
+      </c>
+      <c r="F5" s="3" t="inlineStr">
+        <is>
+          <t>Ticket status</t>
+        </is>
+      </c>
+      <c r="G5" s="3" t="inlineStr">
+        <is>
+          <t>Action</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
           <t>C29373</t>
         </is>
       </c>
-      <c r="B5" s="3" t="inlineStr">
+      <c r="B6" s="4" t="inlineStr">
         <is>
           <t>https://shopview.testrail.io/index.php?/cases/view/29373</t>
         </is>
       </c>
-      <c r="C5" s="3" t="inlineStr">
+      <c r="C6" s="4" t="inlineStr">
         <is>
           <t>Accept Delivery</t>
         </is>
       </c>
-      <c r="D5" s="3" t="inlineStr">
+      <c r="D6" s="4" t="inlineStr">
         <is>
           <t>On the Accept Delivery screen the group of parts with no vendor yet appears at the TOP of the list; the product owner wanted it at the BOTTOM. Reviewed and accepted as a look-only difference (no effect on how it works) — confirm we keep it as-is and change nothing.</t>
         </is>
       </c>
-      <c r="E5" s="3" t="inlineStr">
+      <c r="E6" s="4" t="inlineStr">
         <is>
           <t>SV-7707</t>
         </is>
       </c>
-      <c r="F5" s="3" t="inlineStr">
+      <c r="F6" s="4" t="inlineStr">
         <is>
           <t>DONE</t>
         </is>
       </c>
-      <c r="G5" s="3" t="inlineStr">
-        <is>
-          <t>DECISION</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="3" t="inlineStr">
-        <is>
-          <t>C29375</t>
-        </is>
-      </c>
-      <c r="B6" s="3" t="inlineStr">
-        <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29375</t>
-        </is>
-      </c>
-      <c r="C6" s="3" t="inlineStr">
-        <is>
-          <t>Accept Delivery</t>
-        </is>
-      </c>
-      <c r="D6" s="3" t="inlineStr">
-        <is>
-          <t>Same Accept-Delivery point as C29373 — the position of the no-vendor group and the multi-vendor indicator. Accepted as look-only — confirm keep as-is, no case change.</t>
-        </is>
-      </c>
-      <c r="E6" s="3" t="inlineStr">
-        <is>
-          <t>SV-7707</t>
-        </is>
-      </c>
-      <c r="F6" s="3" t="inlineStr">
-        <is>
-          <t>DONE</t>
-        </is>
-      </c>
-      <c r="G6" s="3" t="inlineStr">
+      <c r="G6" s="4" t="inlineStr">
         <is>
           <t>DECISION</t>
         </is>
@@ -596,72 +571,109 @@
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
+          <t>C29375</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29375</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>Accept Delivery</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>Same Accept-Delivery point as C29373 — the position of the no-vendor group and the multi-vendor indicator. Accepted as look-only — confirm keep as-is, no case change.</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>SV-7707</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>DONE</t>
+        </is>
+      </c>
+      <c r="G7" s="4" t="inlineStr">
+        <is>
+          <t>DECISION</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="5" t="inlineStr">
+        <is>
           <t>C29396</t>
         </is>
       </c>
-      <c r="B7" s="4" t="inlineStr">
+      <c r="B8" s="5" t="inlineStr">
         <is>
           <t>https://shopview.testrail.io/index.php?/cases/view/29396</t>
         </is>
       </c>
-      <c r="C7" s="4" t="inlineStr">
+      <c r="C8" s="5" t="inlineStr">
         <is>
           <t>Review before completion</t>
         </is>
       </c>
-      <c r="D7" s="4" t="inlineStr">
+      <c r="D8" s="5" t="inlineStr">
         <is>
           <t>When 'require review before completion' is on, signing off finishes the work order straight away with no separate 'Reviewed' holding step. Whether invoicing should be blocked until a review happens is a product decision (Milos). Don't finalise this case until that review ticket ships.</t>
         </is>
       </c>
-      <c r="E7" s="4" t="inlineStr">
+      <c r="E8" s="5" t="inlineStr">
         <is>
           <t>SV-7870</t>
         </is>
       </c>
-      <c r="F7" s="4" t="inlineStr">
+      <c r="F8" s="5" t="inlineStr">
         <is>
           <t>NOT DONE (Blocked)</t>
         </is>
       </c>
-      <c r="G7" s="4" t="inlineStr">
+      <c r="G8" s="5" t="inlineStr">
         <is>
           <t>DECISION</t>
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" s="4" t="inlineStr">
+    <row r="9">
+      <c r="A9" s="5" t="inlineStr">
         <is>
           <t>C29404</t>
         </is>
       </c>
-      <c r="B8" s="4" t="inlineStr">
+      <c r="B9" s="5" t="inlineStr">
         <is>
           <t>https://shopview.testrail.io/index.php?/cases/view/29404</t>
         </is>
       </c>
-      <c r="C8" s="4" t="inlineStr">
+      <c r="C9" s="5" t="inlineStr">
         <is>
           <t>Completion screen — Close/Cancel</t>
         </is>
       </c>
-      <c r="D8" s="4" t="inlineStr">
+      <c r="D9" s="5" t="inlineStr">
         <is>
           <t>The 'Close' vs 'Cancel' confirmation pop-up on the completion screens isn't finalised in the design yet, so the exact behaviour isn't defined. Needs Milos to confirm what Close and Cancel should do before the case can state a result.</t>
         </is>
       </c>
-      <c r="E8" s="4" t="inlineStr">
+      <c r="E9" s="5" t="inlineStr">
         <is>
           <t>SV-7710</t>
         </is>
       </c>
-      <c r="F8" s="4" t="inlineStr">
+      <c r="F9" s="5" t="inlineStr">
         <is>
           <t>NOT DONE (Blocked)</t>
         </is>
       </c>
-      <c r="G8" s="4" t="inlineStr">
+      <c r="G9" s="5" t="inlineStr">
         <is>
           <t>DECISION</t>
         </is>
@@ -705,111 +717,111 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="inlineStr">
+      <c r="A4" s="3" t="inlineStr">
         <is>
           <t>Case ID</t>
         </is>
       </c>
-      <c r="B4" s="2" t="inlineStr">
+      <c r="B4" s="3" t="inlineStr">
         <is>
           <t>TestRail link</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
+      <c r="C4" s="3" t="inlineStr">
         <is>
           <t>Area</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="D4" s="3" t="inlineStr">
         <is>
           <t>What needs to change</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="E4" s="3" t="inlineStr">
         <is>
           <t>Driving ticket</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="F4" s="3" t="inlineStr">
         <is>
           <t>Ticket status</t>
         </is>
       </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="G4" s="3" t="inlineStr">
         <is>
           <t>Action</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="4" t="inlineStr">
+      <c r="A5" s="5" t="inlineStr">
         <is>
           <t>C29396</t>
         </is>
       </c>
-      <c r="B5" s="4" t="inlineStr">
+      <c r="B5" s="5" t="inlineStr">
         <is>
           <t>https://shopview.testrail.io/index.php?/cases/view/29396</t>
         </is>
       </c>
-      <c r="C5" s="4" t="inlineStr">
+      <c r="C5" s="5" t="inlineStr">
         <is>
           <t>Review before completion</t>
         </is>
       </c>
-      <c r="D5" s="4" t="inlineStr">
+      <c r="D5" s="5" t="inlineStr">
         <is>
           <t>When 'require review before completion' is on, signing off finishes the work order straight away with no separate 'Reviewed' holding step. Whether invoicing should be blocked until a review happens is a product decision (Milos). Don't finalise this case until that review ticket ships.</t>
         </is>
       </c>
-      <c r="E5" s="4" t="inlineStr">
+      <c r="E5" s="5" t="inlineStr">
         <is>
           <t>SV-7870</t>
         </is>
       </c>
-      <c r="F5" s="4" t="inlineStr">
+      <c r="F5" s="5" t="inlineStr">
         <is>
           <t>NOT DONE (Blocked)</t>
         </is>
       </c>
-      <c r="G5" s="4" t="inlineStr">
+      <c r="G5" s="5" t="inlineStr">
         <is>
           <t>DECISION</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="4" t="inlineStr">
+      <c r="A6" s="5" t="inlineStr">
         <is>
           <t>C29404</t>
         </is>
       </c>
-      <c r="B6" s="4" t="inlineStr">
+      <c r="B6" s="5" t="inlineStr">
         <is>
           <t>https://shopview.testrail.io/index.php?/cases/view/29404</t>
         </is>
       </c>
-      <c r="C6" s="4" t="inlineStr">
+      <c r="C6" s="5" t="inlineStr">
         <is>
           <t>Completion screen — Close/Cancel</t>
         </is>
       </c>
-      <c r="D6" s="4" t="inlineStr">
+      <c r="D6" s="5" t="inlineStr">
         <is>
           <t>The 'Close' vs 'Cancel' confirmation pop-up on the completion screens isn't finalised in the design yet, so the exact behaviour isn't defined. Needs Milos to confirm what Close and Cancel should do before the case can state a result.</t>
         </is>
       </c>
-      <c r="E6" s="4" t="inlineStr">
+      <c r="E6" s="5" t="inlineStr">
         <is>
           <t>SV-7710</t>
         </is>
       </c>
-      <c r="F6" s="4" t="inlineStr">
+      <c r="F6" s="5" t="inlineStr">
         <is>
           <t>NOT DONE (Blocked)</t>
         </is>
       </c>
-      <c r="G6" s="4" t="inlineStr">
+      <c r="G6" s="5" t="inlineStr">
         <is>
           <t>DECISION</t>
         </is>

--- a/build/simple-flow/SimpleFlow_SpecRecheck_ChangeList_2026-07-23.xlsx
+++ b/build/simple-flow/SimpleFlow_SpecRecheck_ChangeList_2026-07-23.xlsx
@@ -483,7 +483,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>PROVISIONAL — column D 'What needs to change' is pending a fresh LIVE staging check (needs current cookies); it will be rewritten to observed build behaviour before sign-off.</t>
+          <t>LIVE-BUILD CHECK 2026-07-23: 0 of 4 rows re-verified live on staging (green); the rest are flagged '⏳ LIVE CHECK PENDING' in column D and still need live observation.</t>
         </is>
       </c>
     </row>
@@ -549,7 +549,7 @@
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>On the Accept Delivery screen the group of parts with no vendor yet appears at the TOP of the list; the product owner wanted it at the BOTTOM. Reviewed and accepted as a look-only difference (no effect on how it works) — confirm we keep it as-is and change nothing.</t>
+          <t>⏳ LIVE CHECK PENDING (2026-07-23 run: not yet observed) — prior finding: On the Accept Delivery screen the group of parts with no vendor yet appears at the TOP of the list; the product owner wanted it at the BOTTOM. Reviewed and accepted as a look-only difference (no effect on how it works) — confirm we keep it as-is and change nothing.</t>
         </is>
       </c>
       <c r="E6" s="4" t="inlineStr">
@@ -586,7 +586,7 @@
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>Same Accept-Delivery point as C29373 — the position of the no-vendor group and the multi-vendor indicator. Accepted as look-only — confirm keep as-is, no case change.</t>
+          <t>⏳ LIVE CHECK PENDING (2026-07-23 run: not yet observed) — prior finding: Same Accept-Delivery point as C29373 — the position of the no-vendor group and the multi-vendor indicator. Accepted as look-only — confirm keep as-is, no case change.</t>
         </is>
       </c>
       <c r="E7" s="4" t="inlineStr">
@@ -623,7 +623,7 @@
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>When 'require review before completion' is on, signing off finishes the work order straight away with no separate 'Reviewed' holding step. Whether invoicing should be blocked until a review happens is a product decision (Milos). Don't finalise this case until that review ticket ships.</t>
+          <t>⏳ LIVE CHECK PENDING (2026-07-23 run: not yet observed) — prior finding: When 'require review before completion' is on, signing off finishes the work order straight away with no separate 'Reviewed' holding step. Whether invoicing should be blocked until a review happens is a product decision (Milos). Don't finalise this case until that review ticket ships.</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
@@ -660,7 +660,7 @@
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>The 'Close' vs 'Cancel' confirmation pop-up on the completion screens isn't finalised in the design yet, so the exact behaviour isn't defined. Needs Milos to confirm what Close and Cancel should do before the case can state a result.</t>
+          <t>⏳ LIVE CHECK PENDING (2026-07-23 run: not yet observed) — prior finding: The 'Close' vs 'Cancel' confirmation pop-up on the completion screens isn't finalised in the design yet, so the exact behaviour isn't defined. Needs Milos to confirm what Close and Cancel should do before the case can state a result.</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
@@ -771,7 +771,7 @@
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>When 'require review before completion' is on, signing off finishes the work order straight away with no separate 'Reviewed' holding step. Whether invoicing should be blocked until a review happens is a product decision (Milos). Don't finalise this case until that review ticket ships.</t>
+          <t>⏳ LIVE CHECK PENDING (2026-07-23 run: not yet observed) — prior finding: When 'require review before completion' is on, signing off finishes the work order straight away with no separate 'Reviewed' holding step. Whether invoicing should be blocked until a review happens is a product decision (Milos). Don't finalise this case until that review ticket ships.</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
@@ -808,7 +808,7 @@
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>The 'Close' vs 'Cancel' confirmation pop-up on the completion screens isn't finalised in the design yet, so the exact behaviour isn't defined. Needs Milos to confirm what Close and Cancel should do before the case can state a result.</t>
+          <t>⏳ LIVE CHECK PENDING (2026-07-23 run: not yet observed) — prior finding: The 'Close' vs 'Cancel' confirmation pop-up on the completion screens isn't finalised in the design yet, so the exact behaviour isn't defined. Needs Milos to confirm what Close and Cancel should do before the case can state a result.</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">

--- a/build/simple-flow/SimpleFlow_SpecRecheck_ChangeList_2026-07-23.xlsx
+++ b/build/simple-flow/SimpleFlow_SpecRecheck_ChangeList_2026-07-23.xlsx
@@ -483,7 +483,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>LIVE-BUILD CHECK 2026-07-23: 0 of 4 rows re-verified live on staging (green); the rest are flagged '⏳ LIVE CHECK PENDING' in column D and still need live observation.</t>
+          <t>LIVE-BUILD CHECK 2026-07-23: 0 of 4 rows re-verified live on staging (green); 0 characterised-blocked on an env defect (orange, see column D); the rest flagged '⏳ LIVE CHECK PENDING'.</t>
         </is>
       </c>
     </row>

--- a/build/simple-flow/SimpleFlow_SpecRecheck_ChangeList_2026-07-23.xlsx
+++ b/build/simple-flow/SimpleFlow_SpecRecheck_ChangeList_2026-07-23.xlsx
@@ -483,7 +483,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>LIVE-BUILD CHECK 2026-07-23: 0 of 4 rows re-verified live on staging (green); 0 characterised-blocked on an env defect (orange, see column D); the rest flagged '⏳ LIVE CHECK PENDING'.</t>
+          <t>LIVE-BUILD CHECK 2026-07-23: 0 of 4 rows re-verified live (green); 0 confirmed DEVIATION needing a decision; 0 env-blocked; the rest flagged '⏳ LIVE CHECK PENDING'.</t>
         </is>
       </c>
     </row>
